--- a/daily_matches/job_matches_2026-09-12.xlsx
+++ b/daily_matches/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps / Cloud / SRE Engineer, Senior AI / Machine Learning Engineer, Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, Data Lake, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a42c0ea26c495</t>
+          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, Databricks, MongoDB, NoSQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Glue</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393f62b59716a5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHS Corporate</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cedar Creek, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Tableau, Power BI, Matplotlib</t>
+          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241a98c83f3afcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer Engineer II</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41243306ce182728</t>
+          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Advanced Analyst II</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meijer</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Power BI</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f16af799ff179bc</t>
+          <t>https://www.indeed.com/viewjob?jk=13ca5da6412eeabd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Korean Bilingual Sr. AI DevOps Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13143fdb598a9097</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6053cc92e634a9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Apache Airflow, CI/CD, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e60cd51a5aabad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec83d6d7be080934</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, MLflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3652398c2da933ad</t>
+          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad94608c8ee3b44</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2c47264765b599</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>AI Engineer with Computer Vision</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Gemini, FAISS, Pinecone, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c15ef63631c4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb30e1763f648406</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Research Computing Engineer (AI Infrastructure and HPC)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Penn State University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>University Park, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83911edc8cd15ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0246c9e9dc153db</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Research Computing Engineer (AI Infrastructure and HPC)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Penn State University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>University Park, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccc8d9e9a5c075a</t>
+          <t>https://www.indeed.com/viewjob?jk=62170d1ce5936ff5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Terraform, Git, Snowflake, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30483a1036fbe4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Viking Cruises</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, Synapse, Databricks, Kafka, Hadoop, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ba4701a18ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e4bb2bd7ee928d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b84f98d039d55d6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Prototyping &amp; Transformation Associate</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,462 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a834c10292738b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7252eb1b333304</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scientist- Data and Modeler II USA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=443d3e1b1bd2c0ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mid-Level Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, Git, Databricks, PySpark, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdc5aa52419926b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst - Tableau Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KeyBank</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a723c41898322b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst - Tableau Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KeyBank</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brooklyn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccabd383cb8af65d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Corteva Agriscience</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da4899f2a98ae3d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer II Data Reliability &amp; Automation (APIs)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sony Interactive Entertainment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Terraform, Kafka, Cassandra, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a5d4a4932ae475f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer - Guardrails and Observability</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, XGBoost, Keras, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93fcca6499dccc89</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a5e6f82b1d6a28b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Engineer - Monitoring, Observability, and Governance</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d992d31467f41bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d80bf289fcc547d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Web Marketing Program - Digital Experience Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, PyTorch, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9468d58f6a9a0a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Investment Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Colorado Public Employees' Retirement Association</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Athena, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c368be9d6998365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Quality Control Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rensselaer, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cb642a3f9b4004c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=679e32885e3f74d9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-12.xlsx
+++ b/daily_matches/job_matches_2026-09-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>43.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, Data Lake, MLflow</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438f50351525893</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc0184eaf514f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Junior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4c0de94ab1dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=24a3e16353933b0a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Applied AI/ML Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Glue</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,172 +566,172 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5019aa8fc4cc7d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c35b5887316734</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>State Teachers' Retirement System</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Creek, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Power BI</t>
+          <t>RAG, Prompt Engineering, YOLO, Glue, Redshift, CI/CD, Snowflake, Redshift, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b1a0c64bfead5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Software Engineer III - Agentic AI, Java/Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303d9eb6bc810a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e520441c4192543</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Software Engineer, ML Ops</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, Copilot, PyTorch, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ca5da6412eeabd</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Python</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6053cc92e634a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8b736c7ebdb7576d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Python</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec83d6d7be080934</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Software Engineer III - Java/AWS/Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, MLflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, S3, CI/CD, Terraform, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e42cfd58bc1a82</t>
+          <t>https://www.indeed.com/viewjob?jk=25cd53664b78d134</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>HGB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Python, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2c47264765b599</t>
+          <t>https://www.indeed.com/viewjob?jk=0e44fdf01fb7ece9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer with Computer Vision</t>
+          <t>Sr. Data Analyst - Tableau Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Gemini, FAISS, Pinecone, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,137 +846,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb30e1763f648406</t>
+          <t>https://www.indeed.com/viewjob?jk=71cd13e45984ea52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research Computing Engineer (AI Infrastructure and HPC)</t>
+          <t>Software Engineer III - GenAI Patterns</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>University Park, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0246c9e9dc153db</t>
+          <t>https://www.indeed.com/viewjob?jk=02eb6f6927ce6287</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Research Computing Engineer (AI Infrastructure and HPC)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>University Park, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170d1ce5936ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=3377c0914473422c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
+          <t>Senior Software Engineer - C++/Python</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, SQL, R, C++, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35b58795197a9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=929954a666211499</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI and ML Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viking Cruises</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Databricks, Kafka, Hadoop, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,532 +986,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437f5637a1d18c13</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fac8d604f5bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer - Fraud</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, XGBoost, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b84f98d039d55d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7252eb1b333304</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Alignment Health</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=443d3e1b1bd2c0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mid-Level Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, XGBoost, Git, Databricks, PySpark, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc5aa52419926b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>KeyBank</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a723c41898322b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>KeyBank</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brooklyn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccabd383cb8af65d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Corteva Agriscience</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da4899f2a98ae3d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer II Data Reliability &amp; Automation (APIs)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Sony Interactive Entertainment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, Terraform, Kafka, Cassandra, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a5d4a4932ae475f</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer - Guardrails and Observability</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e6f82b1d6a28b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Engineer - Monitoring, Observability, and Governance</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d992d31467f41bfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Information Technology Senior Management Forum</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d80bf289fcc547d</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Web Marketing Program - Digital Experience Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, PyTorch, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9468d58f6a9a0a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Investment Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Colorado Public Employees' Retirement Association</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Athena, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c368be9d6998365d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Quality Control Data Scientist</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Regeneron</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rensselaer, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb642a3f9b4004c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=679e32885e3f74d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d59964b4195fa8</t>
         </is>
       </c>
     </row>
